--- a/restaurant_manager_forms/008_employee_peer_review_template--restaurant_manager_forms.xlsx
+++ b/restaurant_manager_forms/008_employee_peer_review_template--restaurant_manager_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -734,8 +734,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'review_and_give_feedback',_'value':_'review_and_give_feedback'}</t>
+          <t>review_and_give_feedback</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'review and give feedback', 'value': 'review and give feedback'}</t>
+          <t>review and give feedback</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'create_an_action_plan',_'value':_'create_an_action_plan'}</t>
+          <t>create_an_action_plan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'create an action plan', 'value': 'create an action plan'}</t>
+          <t>create an action plan</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'recognize_and_reward',_'value':_'recognize_and_reward'}</t>
+          <t>recognize_and_reward</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'recognize and reward', 'value': 'recognize and reward'}</t>
+          <t>recognize and reward</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'other', 'value': 'other'}</t>
+          <t>other</t>
         </is>
       </c>
     </row>
